--- a/out/fy26/WineBank_FY2026_着地予想.xlsx
+++ b/out/fy26/WineBank_FY2026_着地予想.xlsx
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="C6" s="7">
-        <f>SUM('②月次推移表'!C22:L22)+'③前提'!$C$15</f>
+        <f>SUM('②月次推移表'!C23:L23)+'③前提'!$C$15</f>
         <v/>
       </c>
       <c r="D6" s="8">
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="C7" s="10">
-        <f>SUM('②月次推移表'!M22:N22)-'③前提'!$C$15-'③前提'!$D$24</f>
+        <f>SUM('②月次推移表'!M23:N23)-'③前提'!$C$15-'③前提'!$D$24</f>
         <v/>
       </c>
       <c r="D7" s="8">
@@ -666,7 +666,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>私募3号70＋4号5＋M&amp;A仲介20＋コンサル料10＝105百万円</t>
+          <t>私募 現物出資30＋売上計上45＋M&amp;A仲介20＋コンサル料10＝105百万円</t>
         </is>
       </c>
     </row>
@@ -745,11 +745,11 @@
         </is>
       </c>
       <c r="C14" s="10">
-        <f>SUM('②月次推移表'!C15:L15)</f>
+        <f>SUM('②月次推移表'!C16:L16)</f>
         <v/>
       </c>
       <c r="D14" s="10">
-        <f>SUM('②月次推移表'!M15:N15)</f>
+        <f>SUM('②月次推移表'!M16:N16)</f>
         <v/>
       </c>
       <c r="E14" s="8">
@@ -764,11 +764,11 @@
         </is>
       </c>
       <c r="C15" s="16">
-        <f>SUM('②月次推移表'!C16:L16)</f>
+        <f>SUM('②月次推移表'!C17:L17)</f>
         <v/>
       </c>
       <c r="D15" s="16">
-        <f>SUM('②月次推移表'!M16:N16)</f>
+        <f>SUM('②月次推移表'!M17:N17)</f>
         <v/>
       </c>
       <c r="E15" s="13">
@@ -783,11 +783,11 @@
         </is>
       </c>
       <c r="C16" s="10">
-        <f>SUM('②月次推移表'!C21:L21)</f>
+        <f>SUM('②月次推移表'!C22:L22)</f>
         <v/>
       </c>
       <c r="D16" s="10">
-        <f>SUM('②月次推移表'!M21:N21)</f>
+        <f>SUM('②月次推移表'!M22:N22)</f>
         <v/>
       </c>
       <c r="E16" s="8">
@@ -802,11 +802,11 @@
         </is>
       </c>
       <c r="C17" s="16">
-        <f>SUM('②月次推移表'!C22:L22)</f>
+        <f>SUM('②月次推移表'!C23:L23)</f>
         <v/>
       </c>
       <c r="D17" s="16">
-        <f>SUM('②月次推移表'!M22:N22)</f>
+        <f>SUM('②月次推移表'!M23:N23)</f>
         <v/>
       </c>
       <c r="E17" s="13">
@@ -821,11 +821,11 @@
         </is>
       </c>
       <c r="C18" s="10">
-        <f>SUM('②月次推移表'!C23:L23)</f>
+        <f>SUM('②月次推移表'!C24:L24)</f>
         <v/>
       </c>
       <c r="D18" s="10">
-        <f>SUM('②月次推移表'!M23:N23)</f>
+        <f>SUM('②月次推移表'!M24:N24)</f>
         <v/>
       </c>
       <c r="E18" s="8">
@@ -840,11 +840,11 @@
         </is>
       </c>
       <c r="C19" s="10">
-        <f>SUM('②月次推移表'!C24:L24)</f>
+        <f>SUM('②月次推移表'!C25:L25)</f>
         <v/>
       </c>
       <c r="D19" s="10">
-        <f>SUM('②月次推移表'!M24:N24)</f>
+        <f>SUM('②月次推移表'!M25:N25)</f>
         <v/>
       </c>
       <c r="E19" s="8">
@@ -859,11 +859,11 @@
         </is>
       </c>
       <c r="C20" s="16">
-        <f>SUM('②月次推移表'!C25:L25)</f>
+        <f>SUM('②月次推移表'!C26:L26)</f>
         <v/>
       </c>
       <c r="D20" s="16">
-        <f>SUM('②月次推移表'!M25:N25)</f>
+        <f>SUM('②月次推移表'!M26:N26)</f>
         <v/>
       </c>
       <c r="E20" s="13">
@@ -977,7 +977,7 @@
       </c>
       <c r="C30" s="22" t="inlineStr">
         <is>
-          <t>2026/07末の商品は721,162,328円。私募2本の原価525百万円を在庫から出庫する場合、9月末は約196百万円まで減ります。従来のFY2027モデルの期首在庫420百万円とは差があります。</t>
+          <t>2026/07末の商品は721,162,328円。8-9月の仕入55百万円を見込んでも、私募の売上計上分（原価255百万円）と現物出資分（簿価270百万円）が抜けるため、9月末は約187百万円まで減ります。従来のFY2027モデルの期首在庫420百万円とは大きく異なります。</t>
         </is>
       </c>
     </row>
@@ -989,7 +989,7 @@
       </c>
       <c r="C31" s="22" t="inlineStr">
         <is>
-          <t>課税売上高が1,190百万円前後まで増えるため、FY2026分の確定納付額が従来想定より増えます。FY2027の資金繰りに影響するため、翌期PLの作成時に織り込みます。</t>
+          <t>課税売上高は890百万円前後です。現物出資分3億円は売上計上しませんが、消費税法上は資産の譲渡等に該当し課税対象となる可能性があります。FY2026分の確定納付額に影響するため、顧問税理士にご確認ください。</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E33"/>
+  <dimension ref="B1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2026/04-07実績の月平均25,624,504円</t>
+          <t>2026/04-07実績の月平均25,624,504円。貴社ご指定によりフラット</t>
         </is>
       </c>
     </row>
@@ -1225,36 +1225,36 @@
     <row r="20">
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>① 私募ファンド3号</t>
+          <t>① 私募（現物出資分）※売上計上なし</t>
         </is>
       </c>
       <c r="C20" s="18" t="n">
-        <v>500000000</v>
+        <v>0</v>
       </c>
       <c r="D20" s="18" t="n">
-        <v>70000000</v>
+        <v>30000000</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9月末に組成完了。粗利60百万円＋販売手数料10百万円</t>
+          <t>★3億円は現物出資のため売上を計上せず、粗利30百万円（P2から10＋WineBankから20）のみ計上。売上原価のマイナスとして処理</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>② 私募ファンド4号</t>
+          <t>② 私募（売上計上分）</t>
         </is>
       </c>
       <c r="C21" s="18" t="n">
-        <v>100000000</v>
+        <v>300000000</v>
       </c>
       <c r="D21" s="18" t="n">
-        <v>5000000</v>
+        <v>45000000</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>同上。粗利率5%</t>
+          <t>3億円を売上計上。粗利45百万円（粗利率15.0%）</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>粗利105,000,000円。原価は売上−粗利＝525,000,000円</t>
+          <t>粗利105,000,000円は従来想定と同額。売上は630→330百万円に減少（現物出資分3億を売上計上しないため）</t>
         </is>
       </c>
     </row>
@@ -1346,57 +1346,111 @@
         </is>
       </c>
       <c r="C28" s="18" t="n">
-        <v>0</v>
+        <v>55000000</v>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>★8-9月の仕入予定額をご入力ください</t>
+          <t>貴社ご指定：50〜60百万円。中央値55百万円</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>2026/08-09 売上原価（出庫）</t>
+          <t>2026/08-09 売上原価による出庫</t>
         </is>
       </c>
       <c r="C29" s="8">
-        <f>SUM('②月次推移表'!M15:N15)</f>
+        <f>SUM('②月次推移表'!M13:N13)+SUM('②月次推移表'!M14:N14)</f>
         <v/>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>②月次推移表の8月・9月の売上原価 合計</t>
+          <t>既存事業の8-9月＋私募（売上計上分）の原価。現物出資の評価差額は含まない</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="9" t="inlineStr">
         <is>
+          <t>現物出資 出資額（評価額）</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="n">
+        <v>300000000</v>
+      </c>
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>★現物出資した金額。売上には計上しません</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　うち 評価差額（粗利計上分）</t>
+        </is>
+      </c>
+      <c r="C31" s="8">
+        <f>D20</f>
+        <v/>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>【3】①の粗利30,000,000円</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>現物出資による在庫の振替（簿価）</t>
+        </is>
+      </c>
+      <c r="C32" s="8">
+        <f>C30-C31</f>
+        <v/>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>出資額−評価差額。売上原価ではなく投資その他の資産へ振替</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="9" t="inlineStr">
+        <is>
           <t>2026/09末 商品（見込）</t>
         </is>
       </c>
-      <c r="C30" s="21">
-        <f>C27+C28-C29</f>
-        <v/>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>期首＋仕入−出庫</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="14" t="inlineStr">
-        <is>
-          <t>※私募ファンドの原価525百万円を在庫から出庫する場合、9月末の商品在庫は約196百万円まで減ります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="14" t="inlineStr">
-        <is>
-          <t>※従来のFY2027モデルは期首在庫420百万円を前提としていました。ここが変わると来期の仕入計画と資金繰りに影響します。</t>
+      <c r="C33" s="21">
+        <f>C27+C28-C29-C32</f>
+        <v/>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>期首＋仕入−出庫−現物出資の振替</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>※現物出資したワインは売上原価にはならず、簿価のまま投資その他の資産へ振り替わります。在庫からは出ますが損益には出ません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>※従来のFY2027モデルは期首在庫420百万円・2026/09に在庫200百万円を販売してみずほ銀行へ返済、という前提でした。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　今回の私募（現物出資300＋売上計上300）はそれより大きい取引のため、期首在庫の前提を置き直す必要があります。</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:O32"/>
+  <dimension ref="B1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1590,7 +1644,7 @@
     <row r="7">
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">　＋私募ファンド3号</t>
+          <t xml:space="preserve">　＋私募（現物出資分）※売上計上なし</t>
         </is>
       </c>
       <c r="C7" s="30" t="n">
@@ -1638,7 +1692,7 @@
     <row r="8">
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">　＋私募ファンド4号</t>
+          <t xml:space="preserve">　＋私募（売上計上分）</t>
         </is>
       </c>
       <c r="C8" s="30" t="n">
@@ -1910,7 +1964,7 @@
     <row r="14">
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">　＋私募ファンド 原価</t>
+          <t xml:space="preserve">　＋上乗せ案件 原価（売上計上分）</t>
         </is>
       </c>
       <c r="C14" s="30" t="n">
@@ -1947,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="31">
-        <f>('③前提'!$C$20-'③前提'!$D$20)+('③前提'!$C$21-'③前提'!$D$21)</f>
+        <f>SUM('③前提'!$C$21,'③前提'!$C$22,'③前提'!$C$23)-SUM('③前提'!$D$21,'③前提'!$D$22,'③前提'!$D$23)</f>
         <v/>
       </c>
       <c r="O14" s="8">
@@ -1956,293 +2010,292 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="32" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　＋現物出資 評価差額（原価のマイナス）</t>
+        </is>
+      </c>
+      <c r="C15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="31">
+        <f>-'③前提'!$D$20</f>
+        <v/>
+      </c>
+      <c r="O15" s="8">
+        <f>SUM(C15:N15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="32" t="inlineStr">
         <is>
           <t>売上原価 合計</t>
         </is>
       </c>
-      <c r="C15" s="33">
-        <f>C13+C14</f>
-        <v/>
-      </c>
-      <c r="D15" s="33">
-        <f>D13+D14</f>
-        <v/>
-      </c>
-      <c r="E15" s="33">
-        <f>E13+E14</f>
-        <v/>
-      </c>
-      <c r="F15" s="33">
-        <f>F13+F14</f>
-        <v/>
-      </c>
-      <c r="G15" s="33">
-        <f>G13+G14</f>
-        <v/>
-      </c>
-      <c r="H15" s="33">
-        <f>H13+H14</f>
-        <v/>
-      </c>
-      <c r="I15" s="33">
-        <f>I13+I14</f>
-        <v/>
-      </c>
-      <c r="J15" s="33">
-        <f>J13+J14</f>
-        <v/>
-      </c>
-      <c r="K15" s="33">
-        <f>K13+K14</f>
-        <v/>
-      </c>
-      <c r="L15" s="33">
-        <f>L13+L14</f>
-        <v/>
-      </c>
-      <c r="M15" s="33">
-        <f>M13+M14</f>
-        <v/>
-      </c>
-      <c r="N15" s="33">
-        <f>N13+N14</f>
-        <v/>
-      </c>
-      <c r="O15" s="33">
-        <f>SUM(C15:N15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="11" t="inlineStr">
+      <c r="C16" s="33">
+        <f>C13+C14+C15</f>
+        <v/>
+      </c>
+      <c r="D16" s="33">
+        <f>D13+D14+D15</f>
+        <v/>
+      </c>
+      <c r="E16" s="33">
+        <f>E13+E14+E15</f>
+        <v/>
+      </c>
+      <c r="F16" s="33">
+        <f>F13+F14+F15</f>
+        <v/>
+      </c>
+      <c r="G16" s="33">
+        <f>G13+G14+G15</f>
+        <v/>
+      </c>
+      <c r="H16" s="33">
+        <f>H13+H14+H15</f>
+        <v/>
+      </c>
+      <c r="I16" s="33">
+        <f>I13+I14+I15</f>
+        <v/>
+      </c>
+      <c r="J16" s="33">
+        <f>J13+J14+J15</f>
+        <v/>
+      </c>
+      <c r="K16" s="33">
+        <f>K13+K14+K15</f>
+        <v/>
+      </c>
+      <c r="L16" s="33">
+        <f>L13+L14+L15</f>
+        <v/>
+      </c>
+      <c r="M16" s="33">
+        <f>M13+M14+M15</f>
+        <v/>
+      </c>
+      <c r="N16" s="33">
+        <f>N13+N14+N15</f>
+        <v/>
+      </c>
+      <c r="O16" s="33">
+        <f>SUM(C16:N16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>売上総利益</t>
         </is>
       </c>
-      <c r="C16" s="21">
-        <f>C11-C15</f>
-        <v/>
-      </c>
-      <c r="D16" s="21">
-        <f>D11-D15</f>
-        <v/>
-      </c>
-      <c r="E16" s="21">
-        <f>E11-E15</f>
-        <v/>
-      </c>
-      <c r="F16" s="21">
-        <f>F11-F15</f>
-        <v/>
-      </c>
-      <c r="G16" s="21">
-        <f>G11-G15</f>
-        <v/>
-      </c>
-      <c r="H16" s="21">
-        <f>H11-H15</f>
-        <v/>
-      </c>
-      <c r="I16" s="21">
-        <f>I11-I15</f>
-        <v/>
-      </c>
-      <c r="J16" s="21">
-        <f>J11-J15</f>
-        <v/>
-      </c>
-      <c r="K16" s="21">
-        <f>K11-K15</f>
-        <v/>
-      </c>
-      <c r="L16" s="21">
-        <f>L11-L15</f>
-        <v/>
-      </c>
-      <c r="M16" s="21">
-        <f>M11-M15</f>
-        <v/>
-      </c>
-      <c r="N16" s="21">
-        <f>N11-N15</f>
-        <v/>
-      </c>
-      <c r="O16" s="21">
-        <f>SUM(C16:N16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="9" t="inlineStr">
+      <c r="C17" s="21">
+        <f>C11-C16</f>
+        <v/>
+      </c>
+      <c r="D17" s="21">
+        <f>D11-D16</f>
+        <v/>
+      </c>
+      <c r="E17" s="21">
+        <f>E11-E16</f>
+        <v/>
+      </c>
+      <c r="F17" s="21">
+        <f>F11-F16</f>
+        <v/>
+      </c>
+      <c r="G17" s="21">
+        <f>G11-G16</f>
+        <v/>
+      </c>
+      <c r="H17" s="21">
+        <f>H11-H16</f>
+        <v/>
+      </c>
+      <c r="I17" s="21">
+        <f>I11-I16</f>
+        <v/>
+      </c>
+      <c r="J17" s="21">
+        <f>J11-J16</f>
+        <v/>
+      </c>
+      <c r="K17" s="21">
+        <f>K11-K16</f>
+        <v/>
+      </c>
+      <c r="L17" s="21">
+        <f>L11-L16</f>
+        <v/>
+      </c>
+      <c r="M17" s="21">
+        <f>M11-M16</f>
+        <v/>
+      </c>
+      <c r="N17" s="21">
+        <f>N11-N16</f>
+        <v/>
+      </c>
+      <c r="O17" s="21">
+        <f>SUM(C17:N17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">　粗利率</t>
         </is>
       </c>
-      <c r="C17" s="17">
-        <f>IF(C11=0,0,C16/C11)</f>
-        <v/>
-      </c>
-      <c r="D17" s="17">
-        <f>IF(D11=0,0,D16/D11)</f>
-        <v/>
-      </c>
-      <c r="E17" s="17">
-        <f>IF(E11=0,0,E16/E11)</f>
-        <v/>
-      </c>
-      <c r="F17" s="17">
-        <f>IF(F11=0,0,F16/F11)</f>
-        <v/>
-      </c>
-      <c r="G17" s="17">
-        <f>IF(G11=0,0,G16/G11)</f>
-        <v/>
-      </c>
-      <c r="H17" s="17">
-        <f>IF(H11=0,0,H16/H11)</f>
-        <v/>
-      </c>
-      <c r="I17" s="17">
-        <f>IF(I11=0,0,I16/I11)</f>
-        <v/>
-      </c>
-      <c r="J17" s="17">
-        <f>IF(J11=0,0,J16/J11)</f>
-        <v/>
-      </c>
-      <c r="K17" s="17">
-        <f>IF(K11=0,0,K16/K11)</f>
-        <v/>
-      </c>
-      <c r="L17" s="17">
-        <f>IF(L11=0,0,L16/L11)</f>
-        <v/>
-      </c>
-      <c r="M17" s="17">
-        <f>IF(M11=0,0,M16/M11)</f>
-        <v/>
-      </c>
-      <c r="N17" s="17">
-        <f>IF(N11=0,0,N16/N11)</f>
-        <v/>
-      </c>
-      <c r="O17" s="34">
-        <f>O16/O11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="28" t="inlineStr">
+      <c r="C18" s="17">
+        <f>IF(C11=0,0,C17/C11)</f>
+        <v/>
+      </c>
+      <c r="D18" s="17">
+        <f>IF(D11=0,0,D17/D11)</f>
+        <v/>
+      </c>
+      <c r="E18" s="17">
+        <f>IF(E11=0,0,E17/E11)</f>
+        <v/>
+      </c>
+      <c r="F18" s="17">
+        <f>IF(F11=0,0,F17/F11)</f>
+        <v/>
+      </c>
+      <c r="G18" s="17">
+        <f>IF(G11=0,0,G17/G11)</f>
+        <v/>
+      </c>
+      <c r="H18" s="17">
+        <f>IF(H11=0,0,H17/H11)</f>
+        <v/>
+      </c>
+      <c r="I18" s="17">
+        <f>IF(I11=0,0,I17/I11)</f>
+        <v/>
+      </c>
+      <c r="J18" s="17">
+        <f>IF(J11=0,0,J17/J11)</f>
+        <v/>
+      </c>
+      <c r="K18" s="17">
+        <f>IF(K11=0,0,K17/K11)</f>
+        <v/>
+      </c>
+      <c r="L18" s="17">
+        <f>IF(L11=0,0,L17/L11)</f>
+        <v/>
+      </c>
+      <c r="M18" s="17">
+        <f>IF(M11=0,0,M17/M11)</f>
+        <v/>
+      </c>
+      <c r="N18" s="17">
+        <f>IF(N11=0,0,N17/N11)</f>
+        <v/>
+      </c>
+      <c r="O18" s="34">
+        <f>O17/O11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>【販売費及び一般管理費】</t>
         </is>
       </c>
-      <c r="C18" s="29" t="n"/>
-      <c r="D18" s="29" t="n"/>
-      <c r="E18" s="29" t="n"/>
-      <c r="F18" s="29" t="n"/>
-      <c r="G18" s="29" t="n"/>
-      <c r="H18" s="29" t="n"/>
-      <c r="I18" s="29" t="n"/>
-      <c r="J18" s="29" t="n"/>
-      <c r="K18" s="29" t="n"/>
-      <c r="L18" s="29" t="n"/>
-      <c r="M18" s="29" t="n"/>
-      <c r="N18" s="29" t="n"/>
-      <c r="O18" s="29" t="n"/>
-    </row>
-    <row r="19">
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>販管費</t>
-        </is>
-      </c>
-      <c r="C19" s="30" t="n">
-        <v>25364892</v>
-      </c>
-      <c r="D19" s="30" t="n">
-        <v>30953282</v>
-      </c>
-      <c r="E19" s="30" t="n">
-        <v>38562456</v>
-      </c>
-      <c r="F19" s="30" t="n">
-        <v>33751779</v>
-      </c>
-      <c r="G19" s="30" t="n">
-        <v>34123901</v>
-      </c>
-      <c r="H19" s="30" t="n">
-        <v>38727868</v>
-      </c>
-      <c r="I19" s="30" t="n">
-        <v>26296530</v>
-      </c>
-      <c r="J19" s="30" t="n">
-        <v>25207614</v>
-      </c>
-      <c r="K19" s="30" t="n">
-        <v>26797697</v>
-      </c>
-      <c r="L19" s="30" t="n">
-        <v>24196173</v>
-      </c>
-      <c r="M19" s="31">
-        <f>'③前提'!$C$7</f>
-        <v/>
-      </c>
-      <c r="N19" s="31">
-        <f>'③前提'!$C$8</f>
-        <v/>
-      </c>
-      <c r="O19" s="8">
-        <f>SUM(C19:N19)</f>
-        <v/>
-      </c>
+      <c r="C19" s="29" t="n"/>
+      <c r="D19" s="29" t="n"/>
+      <c r="E19" s="29" t="n"/>
+      <c r="F19" s="29" t="n"/>
+      <c r="G19" s="29" t="n"/>
+      <c r="H19" s="29" t="n"/>
+      <c r="I19" s="29" t="n"/>
+      <c r="J19" s="29" t="n"/>
+      <c r="K19" s="29" t="n"/>
+      <c r="L19" s="29" t="n"/>
+      <c r="M19" s="29" t="n"/>
+      <c r="N19" s="29" t="n"/>
+      <c r="O19" s="29" t="n"/>
     </row>
     <row r="20">
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">　7月末までの修正（戻し）</t>
+          <t>販管費</t>
         </is>
       </c>
       <c r="C20" s="30" t="n">
-        <v>0</v>
+        <v>25364892</v>
       </c>
       <c r="D20" s="30" t="n">
-        <v>0</v>
+        <v>30953282</v>
       </c>
       <c r="E20" s="30" t="n">
-        <v>0</v>
+        <v>38562456</v>
       </c>
       <c r="F20" s="30" t="n">
-        <v>0</v>
+        <v>33751779</v>
       </c>
       <c r="G20" s="30" t="n">
-        <v>0</v>
+        <v>34123901</v>
       </c>
       <c r="H20" s="30" t="n">
-        <v>0</v>
+        <v>38727868</v>
       </c>
       <c r="I20" s="30" t="n">
-        <v>0</v>
+        <v>26296530</v>
       </c>
       <c r="J20" s="30" t="n">
-        <v>0</v>
+        <v>25207614</v>
       </c>
       <c r="K20" s="30" t="n">
-        <v>0</v>
+        <v>26797697</v>
       </c>
       <c r="L20" s="30" t="n">
-        <v>0</v>
+        <v>24196173</v>
       </c>
       <c r="M20" s="31">
-        <f>-IF('③前提'!$C$16=8,'③前提'!$C$15,0)</f>
+        <f>'③前提'!$C$7</f>
         <v/>
       </c>
       <c r="N20" s="31">
-        <f>-IF('③前提'!$C$16=9,'③前提'!$C$15,0)</f>
+        <f>'③前提'!$C$8</f>
         <v/>
       </c>
       <c r="O20" s="8">
@@ -2251,166 +2304,168 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="32" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　7月末までの修正（戻し）</t>
+        </is>
+      </c>
+      <c r="C21" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="31">
+        <f>-IF('③前提'!$C$16=8,'③前提'!$C$15,0)</f>
+        <v/>
+      </c>
+      <c r="N21" s="31">
+        <f>-IF('③前提'!$C$16=9,'③前提'!$C$15,0)</f>
+        <v/>
+      </c>
+      <c r="O21" s="8">
+        <f>SUM(C21:N21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="32" t="inlineStr">
         <is>
           <t>販管費 計</t>
         </is>
       </c>
-      <c r="C21" s="33">
-        <f>C19+C20</f>
-        <v/>
-      </c>
-      <c r="D21" s="33">
-        <f>D19+D20</f>
-        <v/>
-      </c>
-      <c r="E21" s="33">
-        <f>E19+E20</f>
-        <v/>
-      </c>
-      <c r="F21" s="33">
-        <f>F19+F20</f>
-        <v/>
-      </c>
-      <c r="G21" s="33">
-        <f>G19+G20</f>
-        <v/>
-      </c>
-      <c r="H21" s="33">
-        <f>H19+H20</f>
-        <v/>
-      </c>
-      <c r="I21" s="33">
-        <f>I19+I20</f>
-        <v/>
-      </c>
-      <c r="J21" s="33">
-        <f>J19+J20</f>
-        <v/>
-      </c>
-      <c r="K21" s="33">
-        <f>K19+K20</f>
-        <v/>
-      </c>
-      <c r="L21" s="33">
-        <f>L19+L20</f>
-        <v/>
-      </c>
-      <c r="M21" s="33">
-        <f>M19+M20</f>
-        <v/>
-      </c>
-      <c r="N21" s="33">
-        <f>N19+N20</f>
-        <v/>
-      </c>
-      <c r="O21" s="33">
-        <f>SUM(C21:N21)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="19" t="inlineStr">
+      <c r="C22" s="33">
+        <f>C20+C21</f>
+        <v/>
+      </c>
+      <c r="D22" s="33">
+        <f>D20+D21</f>
+        <v/>
+      </c>
+      <c r="E22" s="33">
+        <f>E20+E21</f>
+        <v/>
+      </c>
+      <c r="F22" s="33">
+        <f>F20+F21</f>
+        <v/>
+      </c>
+      <c r="G22" s="33">
+        <f>G20+G21</f>
+        <v/>
+      </c>
+      <c r="H22" s="33">
+        <f>H20+H21</f>
+        <v/>
+      </c>
+      <c r="I22" s="33">
+        <f>I20+I21</f>
+        <v/>
+      </c>
+      <c r="J22" s="33">
+        <f>J20+J21</f>
+        <v/>
+      </c>
+      <c r="K22" s="33">
+        <f>K20+K21</f>
+        <v/>
+      </c>
+      <c r="L22" s="33">
+        <f>L20+L21</f>
+        <v/>
+      </c>
+      <c r="M22" s="33">
+        <f>M20+M21</f>
+        <v/>
+      </c>
+      <c r="N22" s="33">
+        <f>N20+N21</f>
+        <v/>
+      </c>
+      <c r="O22" s="33">
+        <f>SUM(C22:N22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>営業利益</t>
         </is>
       </c>
-      <c r="C22" s="13">
-        <f>C16-C21</f>
-        <v/>
-      </c>
-      <c r="D22" s="13">
-        <f>D16-D21</f>
-        <v/>
-      </c>
-      <c r="E22" s="13">
-        <f>E16-E21</f>
-        <v/>
-      </c>
-      <c r="F22" s="13">
-        <f>F16-F21</f>
-        <v/>
-      </c>
-      <c r="G22" s="13">
-        <f>G16-G21</f>
-        <v/>
-      </c>
-      <c r="H22" s="13">
-        <f>H16-H21</f>
-        <v/>
-      </c>
-      <c r="I22" s="13">
-        <f>I16-I21</f>
-        <v/>
-      </c>
-      <c r="J22" s="13">
-        <f>J16-J21</f>
-        <v/>
-      </c>
-      <c r="K22" s="13">
-        <f>K16-K21</f>
-        <v/>
-      </c>
-      <c r="L22" s="13">
-        <f>L16-L21</f>
-        <v/>
-      </c>
-      <c r="M22" s="13">
-        <f>M16-M21</f>
-        <v/>
-      </c>
-      <c r="N22" s="13">
-        <f>N16-N21</f>
-        <v/>
-      </c>
-      <c r="O22" s="13">
-        <f>SUM(C22:N22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>営業外収益</t>
-        </is>
-      </c>
-      <c r="C23" s="30" t="n">
-        <v>240000</v>
-      </c>
-      <c r="D23" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="30" t="n">
-        <v>74699</v>
-      </c>
-      <c r="F23" s="30" t="n">
-        <v>978</v>
-      </c>
-      <c r="G23" s="30" t="n">
-        <v>41468</v>
-      </c>
-      <c r="H23" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="8">
+      <c r="C23" s="13">
+        <f>C17-C22</f>
+        <v/>
+      </c>
+      <c r="D23" s="13">
+        <f>D17-D22</f>
+        <v/>
+      </c>
+      <c r="E23" s="13">
+        <f>E17-E22</f>
+        <v/>
+      </c>
+      <c r="F23" s="13">
+        <f>F17-F22</f>
+        <v/>
+      </c>
+      <c r="G23" s="13">
+        <f>G17-G22</f>
+        <v/>
+      </c>
+      <c r="H23" s="13">
+        <f>H17-H22</f>
+        <v/>
+      </c>
+      <c r="I23" s="13">
+        <f>I17-I22</f>
+        <v/>
+      </c>
+      <c r="J23" s="13">
+        <f>J17-J22</f>
+        <v/>
+      </c>
+      <c r="K23" s="13">
+        <f>K17-K22</f>
+        <v/>
+      </c>
+      <c r="L23" s="13">
+        <f>L17-L22</f>
+        <v/>
+      </c>
+      <c r="M23" s="13">
+        <f>M17-M22</f>
+        <v/>
+      </c>
+      <c r="N23" s="13">
+        <f>N17-N22</f>
+        <v/>
+      </c>
+      <c r="O23" s="13">
         <f>SUM(C23:N23)</f>
         <v/>
       </c>
@@ -2418,46 +2473,44 @@
     <row r="24">
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>営業外費用</t>
+          <t>営業外収益</t>
         </is>
       </c>
       <c r="C24" s="30" t="n">
-        <v>666707</v>
+        <v>240000</v>
       </c>
       <c r="D24" s="30" t="n">
-        <v>638316</v>
+        <v>0</v>
       </c>
       <c r="E24" s="30" t="n">
-        <v>671047</v>
+        <v>74699</v>
       </c>
       <c r="F24" s="30" t="n">
-        <v>561216</v>
+        <v>978</v>
       </c>
       <c r="G24" s="30" t="n">
-        <v>1440650</v>
+        <v>41468</v>
       </c>
       <c r="H24" s="30" t="n">
-        <v>1060679</v>
+        <v>0</v>
       </c>
       <c r="I24" s="30" t="n">
-        <v>1243705</v>
+        <v>0</v>
       </c>
       <c r="J24" s="30" t="n">
-        <v>989178</v>
+        <v>0</v>
       </c>
       <c r="K24" s="30" t="n">
-        <v>1686733</v>
+        <v>0</v>
       </c>
       <c r="L24" s="30" t="n">
-        <v>1373329</v>
-      </c>
-      <c r="M24" s="31">
-        <f>'③前提'!$C$9</f>
-        <v/>
-      </c>
-      <c r="N24" s="31">
-        <f>'③前提'!$C$10</f>
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="M24" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="31" t="n">
+        <v>0</v>
       </c>
       <c r="O24" s="8">
         <f>SUM(C24:N24)</f>
@@ -2465,192 +2518,248 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="19" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>営業外費用</t>
+        </is>
+      </c>
+      <c r="C25" s="30" t="n">
+        <v>666707</v>
+      </c>
+      <c r="D25" s="30" t="n">
+        <v>638316</v>
+      </c>
+      <c r="E25" s="30" t="n">
+        <v>671047</v>
+      </c>
+      <c r="F25" s="30" t="n">
+        <v>561216</v>
+      </c>
+      <c r="G25" s="30" t="n">
+        <v>1440650</v>
+      </c>
+      <c r="H25" s="30" t="n">
+        <v>1060679</v>
+      </c>
+      <c r="I25" s="30" t="n">
+        <v>1243705</v>
+      </c>
+      <c r="J25" s="30" t="n">
+        <v>989178</v>
+      </c>
+      <c r="K25" s="30" t="n">
+        <v>1686733</v>
+      </c>
+      <c r="L25" s="30" t="n">
+        <v>1373329</v>
+      </c>
+      <c r="M25" s="31">
+        <f>'③前提'!$C$9</f>
+        <v/>
+      </c>
+      <c r="N25" s="31">
+        <f>'③前提'!$C$10</f>
+        <v/>
+      </c>
+      <c r="O25" s="8">
+        <f>SUM(C25:N25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="19" t="inlineStr">
         <is>
           <t>経常利益</t>
         </is>
       </c>
-      <c r="C25" s="13">
-        <f>C22+C23-C24</f>
-        <v/>
-      </c>
-      <c r="D25" s="13">
-        <f>D22+D23-D24</f>
-        <v/>
-      </c>
-      <c r="E25" s="13">
-        <f>E22+E23-E24</f>
-        <v/>
-      </c>
-      <c r="F25" s="13">
-        <f>F22+F23-F24</f>
-        <v/>
-      </c>
-      <c r="G25" s="13">
-        <f>G22+G23-G24</f>
-        <v/>
-      </c>
-      <c r="H25" s="13">
-        <f>H22+H23-H24</f>
-        <v/>
-      </c>
-      <c r="I25" s="13">
-        <f>I22+I23-I24</f>
-        <v/>
-      </c>
-      <c r="J25" s="13">
-        <f>J22+J23-J24</f>
-        <v/>
-      </c>
-      <c r="K25" s="13">
-        <f>K22+K23-K24</f>
-        <v/>
-      </c>
-      <c r="L25" s="13">
-        <f>L22+L23-L24</f>
-        <v/>
-      </c>
-      <c r="M25" s="13">
-        <f>M22+M23-M24</f>
-        <v/>
-      </c>
-      <c r="N25" s="13">
-        <f>N22+N23-N24</f>
-        <v/>
-      </c>
-      <c r="O25" s="13">
-        <f>SUM(C25:N25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>営業利益 累計</t>
-        </is>
-      </c>
-      <c r="C27" s="35">
-        <f>C22</f>
-        <v/>
-      </c>
-      <c r="D27" s="35">
-        <f>C27+D22</f>
-        <v/>
-      </c>
-      <c r="E27" s="35">
-        <f>D27+E22</f>
-        <v/>
-      </c>
-      <c r="F27" s="35">
-        <f>E27+F22</f>
-        <v/>
-      </c>
-      <c r="G27" s="35">
-        <f>F27+G22</f>
-        <v/>
-      </c>
-      <c r="H27" s="35">
-        <f>G27+H22</f>
-        <v/>
-      </c>
-      <c r="I27" s="35">
-        <f>H27+I22</f>
-        <v/>
-      </c>
-      <c r="J27" s="35">
-        <f>I27+J22</f>
-        <v/>
-      </c>
-      <c r="K27" s="35">
-        <f>J27+K22</f>
-        <v/>
-      </c>
-      <c r="L27" s="35">
-        <f>K27+L22</f>
-        <v/>
-      </c>
-      <c r="M27" s="35">
-        <f>L27+M22</f>
-        <v/>
-      </c>
-      <c r="N27" s="35">
-        <f>M27+N22</f>
+      <c r="C26" s="13">
+        <f>C23+C24-C25</f>
+        <v/>
+      </c>
+      <c r="D26" s="13">
+        <f>D23+D24-D25</f>
+        <v/>
+      </c>
+      <c r="E26" s="13">
+        <f>E23+E24-E25</f>
+        <v/>
+      </c>
+      <c r="F26" s="13">
+        <f>F23+F24-F25</f>
+        <v/>
+      </c>
+      <c r="G26" s="13">
+        <f>G23+G24-G25</f>
+        <v/>
+      </c>
+      <c r="H26" s="13">
+        <f>H23+H24-H25</f>
+        <v/>
+      </c>
+      <c r="I26" s="13">
+        <f>I23+I24-I25</f>
+        <v/>
+      </c>
+      <c r="J26" s="13">
+        <f>J23+J24-J25</f>
+        <v/>
+      </c>
+      <c r="K26" s="13">
+        <f>K23+K24-K25</f>
+        <v/>
+      </c>
+      <c r="L26" s="13">
+        <f>L23+L24-L25</f>
+        <v/>
+      </c>
+      <c r="M26" s="13">
+        <f>M23+M24-M25</f>
+        <v/>
+      </c>
+      <c r="N26" s="13">
+        <f>N23+N24-N25</f>
+        <v/>
+      </c>
+      <c r="O26" s="13">
+        <f>SUM(C26:N26)</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="6" t="inlineStr">
         <is>
+          <t>営業利益 累計</t>
+        </is>
+      </c>
+      <c r="C28" s="35">
+        <f>C23</f>
+        <v/>
+      </c>
+      <c r="D28" s="35">
+        <f>C28+D23</f>
+        <v/>
+      </c>
+      <c r="E28" s="35">
+        <f>D28+E23</f>
+        <v/>
+      </c>
+      <c r="F28" s="35">
+        <f>E28+F23</f>
+        <v/>
+      </c>
+      <c r="G28" s="35">
+        <f>F28+G23</f>
+        <v/>
+      </c>
+      <c r="H28" s="35">
+        <f>G28+H23</f>
+        <v/>
+      </c>
+      <c r="I28" s="35">
+        <f>H28+I23</f>
+        <v/>
+      </c>
+      <c r="J28" s="35">
+        <f>I28+J23</f>
+        <v/>
+      </c>
+      <c r="K28" s="35">
+        <f>J28+K23</f>
+        <v/>
+      </c>
+      <c r="L28" s="35">
+        <f>K28+L23</f>
+        <v/>
+      </c>
+      <c r="M28" s="35">
+        <f>L28+M23</f>
+        <v/>
+      </c>
+      <c r="N28" s="35">
+        <f>M28+N23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="6" t="inlineStr">
+        <is>
           <t>経常利益 累計</t>
         </is>
       </c>
-      <c r="C28" s="35">
-        <f>C25</f>
-        <v/>
-      </c>
-      <c r="D28" s="35">
-        <f>C28+D25</f>
-        <v/>
-      </c>
-      <c r="E28" s="35">
-        <f>D28+E25</f>
-        <v/>
-      </c>
-      <c r="F28" s="35">
-        <f>E28+F25</f>
-        <v/>
-      </c>
-      <c r="G28" s="35">
-        <f>F28+G25</f>
-        <v/>
-      </c>
-      <c r="H28" s="35">
-        <f>G28+H25</f>
-        <v/>
-      </c>
-      <c r="I28" s="35">
-        <f>H28+I25</f>
-        <v/>
-      </c>
-      <c r="J28" s="35">
-        <f>I28+J25</f>
-        <v/>
-      </c>
-      <c r="K28" s="35">
-        <f>J28+K25</f>
-        <v/>
-      </c>
-      <c r="L28" s="35">
-        <f>K28+L25</f>
-        <v/>
-      </c>
-      <c r="M28" s="35">
-        <f>L28+M25</f>
-        <v/>
-      </c>
-      <c r="N28" s="35">
-        <f>M28+N25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="14" t="inlineStr">
-        <is>
-          <t>※2026/08-09の売上原価は「営業利益トントン」の前提から逆算（売上総利益＝販管費）。</t>
-        </is>
+      <c r="C29" s="35">
+        <f>C26</f>
+        <v/>
+      </c>
+      <c r="D29" s="35">
+        <f>C29+D26</f>
+        <v/>
+      </c>
+      <c r="E29" s="35">
+        <f>D29+E26</f>
+        <v/>
+      </c>
+      <c r="F29" s="35">
+        <f>E29+F26</f>
+        <v/>
+      </c>
+      <c r="G29" s="35">
+        <f>F29+G26</f>
+        <v/>
+      </c>
+      <c r="H29" s="35">
+        <f>G29+H26</f>
+        <v/>
+      </c>
+      <c r="I29" s="35">
+        <f>H29+I26</f>
+        <v/>
+      </c>
+      <c r="J29" s="35">
+        <f>I29+J26</f>
+        <v/>
+      </c>
+      <c r="K29" s="35">
+        <f>J29+K26</f>
+        <v/>
+      </c>
+      <c r="L29" s="35">
+        <f>K29+L26</f>
+        <v/>
+      </c>
+      <c r="M29" s="35">
+        <f>L29+M26</f>
+        <v/>
+      </c>
+      <c r="N29" s="35">
+        <f>M29+N26</f>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>※上乗せ4件はすべて2026/09に計上。粗利105,000,000円・原価525,000,000円。</t>
+          <t>※2026/08-09の売上原価は「営業利益トントン」の前提から逆算（売上総利益＝販管費）。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>※「7月末までの修正（戻し）」は販管費の減少として8月に計上。勘定科目は要確認。</t>
+          <t>※上乗せ4件はすべて2026/09に計上。売上330,000,000円・原価225,000,000円・粗利105,000,000円。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>※「7月末までの修正（戻し）」は販管費の減少として2026年8月に計上（貴社ご指定）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>※私募のうち3億円は現物出資のため売上を計上せず、粗利30,000,000円を売上原価のマイナスとして計上しています。</t>
         </is>
       </c>
     </row>
@@ -2737,7 +2846,7 @@
         <v/>
       </c>
       <c r="D6" s="17">
-        <f>(SUM('②月次推移表'!C16:L16)+'③前提'!$C$7+'③前提'!$C$8+'③前提'!$D$24)/C6</f>
+        <f>(SUM('②月次推移表'!C17:L17)+'③前提'!$C$7+'③前提'!$C$8+'③前提'!$D$24)/C6</f>
         <v/>
       </c>
       <c r="E6" s="7">
@@ -2758,7 +2867,7 @@
         <v/>
       </c>
       <c r="D7" s="37">
-        <f>(SUM('②月次推移表'!C16:L16)+'③前提'!$C$7+'③前提'!$C$8+'③前提'!$D$24)/C7</f>
+        <f>(SUM('②月次推移表'!C17:L17)+'③前提'!$C$7+'③前提'!$C$8+'③前提'!$D$24)/C7</f>
         <v/>
       </c>
       <c r="E7" s="21">
@@ -2779,7 +2888,7 @@
         <v/>
       </c>
       <c r="D8" s="17">
-        <f>(SUM('②月次推移表'!C16:L16)+'③前提'!$C$7+'③前提'!$C$8+'③前提'!$D$24)/C8</f>
+        <f>(SUM('②月次推移表'!C17:L17)+'③前提'!$C$7+'③前提'!$C$8+'③前提'!$D$24)/C8</f>
         <v/>
       </c>
       <c r="E8" s="7">
